--- a/results-list/infobae.xlsx
+++ b/results-list/infobae.xlsx
@@ -34,10 +34,9 @@
     <t>https://www.infobae.com/america/agencias/2024/08/09/manos-unidas-apoya-a-pueblos-originarios-del-chaco-paraguayo-acorralados-por-el-agronegocio-y-la-crisis-climatica/</t>
   </si>
   <si>
-    <t xml:space="preserve">**** pais_ag jornal_infobae *ano_2024
-    Manos Unidas apoya a pueblos originarios del Chaco paraguayo "acorralados" por el 'agronegocio' y la crisis climática
-    Manos Unidas apoya a pueblos originarios del Chaco paraguayo "acorralados" por el 'agronegocio' y la crisis climática
-    La organización Manos Unidas acompaña a los pueblos originarios del Chaco paraguayo que se encuentran "acorralados" por el 'agronegocio' y la crisis climática, como ha dado a conocer en el marco del Día Internacional de los Pueblos Indígenas, que se celebra cada 9 de agosto. Como denuncia Manos Unidas, en Paraguay el 2% de la población posee más del 85 % de las tierras cultivables y esta población es uno de los mayores puntos de biodiversidad del planeta. Un ejemplo de ello es la comunidad Payseyamexyempa'a, del pueblo Enxet Sur, ubicada en el Distrito Villa Hayes, en el que las familias se encuentran en una situación de pobreza extrema, a raíz del aislamiento al que están sometidas, rodeadas por fincas de terratenientes. Ante la falta de soluciones a estas situaciones, ya crónicas, Manos Unidas aprobó, el pasado mes de diciembre, la ejecución de un proyecto de doce meses de duración, que beneficiará directamente a 380 personas de cinco comunidades de tres pueblos indígenas diferentes en el municipio de Villa Hayes con un presupuesto de más de 70.000 euros, lo que permitirá la construcción de un depósito para el almacenamiento de lluvia, así como el desarrollo de iniciativas económicas comunitarias ante las escasas oportunidades de desarrollo personal y socio-laboral de los jóvenes indígenas. Como ha detallado la coordinadora ejecutiva de Tierraviva, Lidia Ruiz, estos ciudadanos debe pedir "permiso" para entrar o salir de sus tierras ya que deben usar caminos "privados". "En todos los rincones del país, los grandes propietarios tratan de amedrentar a los indígenas, incluso con personas armadas a su servicio, con la perspectiva de que las comunidades abandonen algún día las tierras en las que viven", ha agregado. Aunque en el suelo chaqueño se llevan a cabo mega proyectos financiados por el estado paraguayo y el sector privado, ninguno de estos atiende a las necesidades de los pueblos indígenas de estos territorios. "Es muy doloroso ver el abandono de los indígenas del Chaco, excluidos de políticas públicas que garanticen sus derechos más básicos, mientras el Gobierno destina enormes inversiones a mega infraestructuras que solo benefician a empresas ganaderas, que a medio plazo provocarán serios daños en las tierras reivindicadas por las comunidades; las mismas comunidades que no tienen acceso a agua potable, a salud, a educación, energía y vías de comunicación", ha añadido Ruiz. Según el responsable de los proyectos de Manos Unidas en Paraguay, Ecuador y Brasil, Carlos Vicente Alconcé, "la causa principal de la violencia hacia las poblaciones indígenas del país es el acaparamiento de tierras por parte de grandes empresas y particulares dedicados al agronegocio". En su opinión, este "fenómeno cíclico" está agravado por la crisis climática "producida, en parte, por la enorme deforestación que realizan ganaderos y grandes propietarios de tierras en el Chaco", por lo que responsabiliza a los diversos gobiernos paraguayos de no tomar cartas en el asunto. "Conocen la realidad por las reiteradas denuncias de las propias comunidades, sin embargo, no hacen nada para atender las necesidades de las familias indígenas", denuncia.</t>
+    <t xml:space="preserve">**** *pais_ag *jornal_infobae *ano_2024
+    Manos Unidas apoya a pueblos originarios del Chaco paraguayo "acorralados" por el 'agronegocio' y la crisis climática. Manos Unidas apoya a pueblos originarios del Chaco paraguayo "acorralados" por el 'agronegocio' y la crisis climática
+. La organización Manos Unidas acompaña a los pueblos originarios del Chaco paraguayo que se encuentran "acorralados" por el 'agronegocio' y la crisis climática, como ha dado a conocer en el marco del Día Internacional de los Pueblos Indígenas, que se celebra cada 9 de agosto. Como denuncia Manos Unidas, en Paraguay el 2% de la población posee más del 85 % de las tierras cultivables y esta población es uno de los mayores puntos de biodiversidad del planeta. Un ejemplo de ello es la comunidad Payseyamexyempa'a, del pueblo Enxet Sur, ubicada en el Distrito Villa Hayes, en el que las familias se encuentran en una situación de pobreza extrema, a raíz del aislamiento al que están sometidas, rodeadas por fincas de terratenientes. Ante la falta de soluciones a estas situaciones, ya crónicas, Manos Unidas aprobó, el pasado mes de diciembre, la ejecución de un proyecto de doce meses de duración, que beneficiará directamente a 380 personas de cinco comunidades de tres pueblos indígenas diferentes en el municipio de Villa Hayes con un presupuesto de más de 70.000 euros, lo que permitirá la construcción de un depósito para el almacenamiento de lluvia, así como el desarrollo de iniciativas económicas comunitarias ante las escasas oportunidades de desarrollo personal y socio-laboral de los jóvenes indígenas. Como ha detallado la coordinadora ejecutiva de Tierraviva, Lidia Ruiz, estos ciudadanos debe pedir "permiso" para entrar o salir de sus tierras ya que deben usar caminos "privados". "En todos los rincones del país, los grandes propietarios tratan de amedrentar a los indígenas, incluso con personas armadas a su servicio, con la perspectiva de que las comunidades abandonen algún día las tierras en las que viven", ha agregado. Aunque en el suelo chaqueño se llevan a cabo mega proyectos financiados por el estado paraguayo y el sector privado, ninguno de estos atiende a las necesidades de los pueblos indígenas de estos territorios. "Es muy doloroso ver el abandono de los indígenas del Chaco, excluidos de políticas públicas que garanticen sus derechos más básicos, mientras el Gobierno destina enormes inversiones a mega infraestructuras que solo benefician a empresas ganaderas, que a medio plazo provocarán serios daños en las tierras reivindicadas por las comunidades; las mismas comunidades que no tienen acceso a agua potable, a salud, a educación, energía y vías de comunicación", ha añadido Ruiz. Según el responsable de los proyectos de Manos Unidas en Paraguay, Ecuador y Brasil, Carlos Vicente Alconcé, "la causa principal de la violencia hacia las poblaciones indígenas del país es el acaparamiento de tierras por parte de grandes empresas y particulares dedicados al agronegocio". En su opinión, este "fenómeno cíclico" está agravado por la crisis climática "producida, en parte, por la enorme deforestación que realizan ganaderos y grandes propietarios de tierras en el Chaco", por lo que responsabiliza a los diversos gobiernos paraguayos de no tomar cartas en el asunto. "Conocen la realidad por las reiteradas denuncias de las propias comunidades, sin embargo, no hacen nada para atender las necesidades de las familias indígenas", denuncia.</t>
   </si>
   <si>
     <t>Podemos pide a Ribera que explique "por qué las ayudas para recuperar el Mar Menor ...</t>
@@ -46,10 +45,9 @@
     <t>https://www.infobae.com/espana/agencias/2024/01/03/podemos-pide-a-ribera-que-explique-por-que-las-ayudas-para-recuperar-el-mar-menor-van-a-multinacionales-de-agronegocio/</t>
   </si>
   <si>
-    <t xml:space="preserve">**** pais_ag jornal_infobae *ano_2024
-    Podemos pide a Ribera que explique "por qué las ayudas para recuperar el Mar Menor van a multinacionales de agronegocio"
-    Podemos pide a Ribera que explique "por qué las ayudas para recuperar el Mar Menor van a multinacionales de agronegocio"
-    El diputado nacional de Podemos y coordinador de la formación 'morada' en la Región de Murcia, Javier Sánchez Serna, ha solicitado a la ministra para la Transición Ecológica y el Reto Demográfico, Teresa Ribera, que explique en el Congreso "por qué las ayudas para recuperar el Mar Menor han ido a las multinacionales del agronegocio". En un comunicado, Sánchez Serna ha explicado que la primera convocatoria de ayudas concedidas por la Fundación Biodiversidad, dependiente del Ministerio, para la restauración y mejora ambiental en el ámbito agrícola con el objetivo de avanzar en la recuperación del Mar Menor, ha recaído en "las mismas multinacionales del agronegocio que llevan años contaminándolo". "Esto es una tomadura de pelo para los vecinos del Mar Menor y las personas que llevamos años luchando por su recuperación y por eso desde Podemos vamos a exigir la comparecencia inmediata de la ministra en el Congreso", ha anunciado. Asimismo, el diputado 'morado' ha exigido que estas ayudas "se destinen íntegramente a los proyectos de los colectivos y científicos que llevan años defendiendo la laguna", frente a lo que considera "un intento descarado de 'greenwashing' para comprar una tregua con el sector del agro y con los que han contaminado el Mar Menor".</t>
+    <t xml:space="preserve">**** *pais_ag *jornal_infobae *ano_2024
+    Podemos pide a Ribera que explique "por qué las ayudas para recuperar el Mar Menor van a multinacionales de agronegocio". Podemos pide a Ribera que explique "por qué las ayudas para recuperar el Mar Menor van a multinacionales de agronegocio"
+. El diputado nacional de Podemos y coordinador de la formación 'morada' en la Región de Murcia, Javier Sánchez Serna, ha solicitado a la ministra para la Transición Ecológica y el Reto Demográfico, Teresa Ribera, que explique en el Congreso "por qué las ayudas para recuperar el Mar Menor han ido a las multinacionales del agronegocio". En un comunicado, Sánchez Serna ha explicado que la primera convocatoria de ayudas concedidas por la Fundación Biodiversidad, dependiente del Ministerio, para la restauración y mejora ambiental en el ámbito agrícola con el objetivo de avanzar en la recuperación del Mar Menor, ha recaído en "las mismas multinacionales del agronegocio que llevan años contaminándolo". "Esto es una tomadura de pelo para los vecinos del Mar Menor y las personas que llevamos años luchando por su recuperación y por eso desde Podemos vamos a exigir la comparecencia inmediata de la ministra en el Congreso", ha anunciado. Asimismo, el diputado 'morado' ha exigido que estas ayudas "se destinen íntegramente a los proyectos de los colectivos y científicos que llevan años defendiendo la laguna", frente a lo que considera "un intento descarado de 'greenwashing' para comprar una tregua con el sector del agro y con los que han contaminado el Mar Menor".</t>
   </si>
   <si>
     <t>La visita de Macron a Brasil reaviva el debate sobre el agronegocio en el país</t>
@@ -58,10 +56,9 @@
     <t>https://www.infobae.com/america/america-latina/2024/03/25/la-visita-de-macron-a-brasil-reaviva-el-debate-sobre-el-agronegocio-en-el-pais/</t>
   </si>
   <si>
-    <t xml:space="preserve">**** pais_ag jornal_infobae *ano_2024
-    La visita de Macron a Brasil reaviva el debate sobre el agronegocio en el país
-    El viaje despertó mucha expectativa por el asunto que ha enfriado las relaciones con Lula en los últimos meses: el acuerdo Unión Europea-Mercosur
-    Brasil es el primer país latinoamericano en recibir al presidente francés Emmanuel Macron desde este martes hasta el 28 de marzo. Los dos presidentes discutirán nuevas asociaciones en áreas como energía, medio ambiente, tecnología y defensa. Juntos inaugurarán la botadura del submarino Tonelero en aguas de Río de Janeiro. El Tonelero es el tercer con propulsión convencional y forma parte del programa de desarrollo de submarinos de Brasil, ProSub, desarrollado en 2008, con un presupuesto de unos 40.000 millones de reales, unos 8.000 millones de dólares. Los dos países iniciaron una asociación estratégica en ese mismo 2008, con Lula y Nicolas Sarkozy a la presidencia. François Hollande fue el último jefe del Elíseo en visitar el gigante latinoamericano en 2016 para los Juegos Olímpicos, ya que en la posterior era Bolsonaro, los ataques del ex presidente brasileño a Macron habían congelado de hecho las relaciones entre los jefes de Estado de ambos países. Por lo tanto, la llegada de Macron también adquiere connotaciones simbólicas desde el punto de vista geopolítico. Sobre todo, hay mucha expectación por el asunto que ha enfriado las relaciones con Lula en los últimos meses: el acuerdo Unión Europea (UE)-Mercosur. Presionado por los agricultores franceses que salieron a la calle, Macron ha dado en los últimos meses un paso atrás decisivo en relación con el acuerdo al insinuar que no se firmará.
+    <t xml:space="preserve">**** *pais_ag *jornal_infobae *ano_2024
+    La visita de Macron a Brasil reaviva el debate sobre el agronegocio en el país. El viaje despertó mucha expectativa por el asunto que ha enfriado las relaciones con Lula en los últimos meses: el acuerdo Unión Europea-Mercosur
+. Brasil es el primer país latinoamericano en recibir al presidente francés Emmanuel Macron desde este martes hasta el 28 de marzo. Los dos presidentes discutirán nuevas asociaciones en áreas como energía, medio ambiente, tecnología y defensa. Juntos inaugurarán la botadura del submarino Tonelero en aguas de Río de Janeiro. El Tonelero es el tercer con propulsión convencional y forma parte del programa de desarrollo de submarinos de Brasil, ProSub, desarrollado en 2008, con un presupuesto de unos 40.000 millones de reales, unos 8.000 millones de dólares. Los dos países iniciaron una asociación estratégica en ese mismo 2008, con Lula y Nicolas Sarkozy a la presidencia. François Hollande fue el último jefe del Elíseo en visitar el gigante latinoamericano en 2016 para los Juegos Olímpicos, ya que en la posterior era Bolsonaro, los ataques del ex presidente brasileño a Macron habían congelado de hecho las relaciones entre los jefes de Estado de ambos países. Por lo tanto, la llegada de Macron también adquiere connotaciones simbólicas desde el punto de vista geopolítico. Sobre todo, hay mucha expectación por el asunto que ha enfriado las relaciones con Lula en los últimos meses: el acuerdo Unión Europea (UE)-Mercosur. Presionado por los agricultores franceses que salieron a la calle, Macron ha dado en los últimos meses un paso atrás decisivo en relación con el acuerdo al insinuar que no se firmará.
 En diciembre pasado, al terminar su presidencia rotativa del Mercosur, el presidente de Brasil, Lula, se había mostrado a la defensiva sobre las posibilidades del acuerdo con la Unión Europea, en discusión desde hacía más de veinte años. “Si no hay acuerdo, paciencia”, había dicho, contradiciendo sus promesas electorales en las que, seguro de un buen resultado, había llegado a plantear la hipótesis de firmar el acuerdo en sus primeros seis meses de presidencia. El bloque comercial latinoamericano formado por Argentina, Brasil, Paraguay y Uruguay se creó en 1991, cuando el comercio entre los miembros del bloque ascendía a 4.500 millones de dólares anuales. 32 años después de su creación, ese comercio asciende a 46.000 millones de dólares por año. Un enorme potencial que, al menos hasta ahora, no se puede aprovechar con Europa. En febrero, al término de una cumbre de la UE, el presidente francés dijo que “seguirá oponiéndose” al acuerdo con Mercosur y declaró que ya había informado al presidente Lula de su posición. También afirmó que “no necesita un acuerdo” para comerciar con América Latina y que cualquier tratado que se plantee debe ser “honesto”.
 Macron, que defiende la “soberanía alimentaria”, criticó que el posible acuerdo permitiría a los productos de Mercosur entrar en el mercado europeo sin las mismas reglas de producción que existen en Francia. Una de sus exigencias es que Europa pueda controlar cómo se lleva a cabo la producción agrícola en Brasil, en términos fitosanitarios y medioambientales, para aceptar que estos productos puedan acceder en el mercado europeo. El motivo del enfrentamiento es la cuestión de la deforestación y su impacto en la vida de las comunidades indígenas.
 Según Francia, a pesar del compromiso del gobierno Lula con las cuestiones ambientales, uno de los problemas de Brasil sigue siendo su dificultad en la metodología para garantizar la preservación. La diplomacia brasileña, por su parte, interpreta la posición de Macron como un intento proteccionista. En ayuda de los brasileños llega ahora un documento de la semana pasada de la Comisión Europea, que defiende que el acuerdo no causará más deforestación. El vicepresidente ejecutivo de la Comisión, Valdis Dombrovskis, en respuesta a una pregunta formulada en enero por el eurodiputado español Miguel Urbán Crespo, del Grupo de Izquierda del Parlamento Europeo, afirmó que “Brasil ha demostrado que puede aumentar la producción mejorando la productividad, sin necesidad de ampliar las tierras agrícolas. Por ejemplo, en el periodo 2005-2012, la producción agrícola brasileña aumentó, mientras que la deforestación y la presión sobre los territorios indígenas disminuyeron significativamente. Por lo tanto, no se espera que el acuerdo genere más presión sobre los territorios indígenas”, dijo Dombrovskis, quien también añadió que “las políticas forestales y de protección indígena son instrumentos clave para mitigar la deforestación y reducir la presión sobre los territorios indígenas”.
@@ -81,10 +78,9 @@
     <t>https://www.infobae.com/america/america-latina/2022/09/25/la-amazonia-y-el-lobby-del-agronegocio-en-el-centro-de-la-campana-electoral-de-brasil/</t>
   </si>
   <si>
-    <t xml:space="preserve">**** pais_ag jornal_infobae *ano_2022
-    La Amazonia y el lobby del agronegocio en el centro de la campaña electoral de Brasil
-    La llamada bancada ruralista ha apoyado a Bolsonaro desde las elecciones de 2018 mientras que Lula agita la causa medioambiental
-    La cuestión medioambiental, por un lado, y el lobby del agronegocio, por otro, han sido la cruz y la alegría del gobierno de Bolsonaro y vuelven a salir, inevitablemente, a la luz en esta campaña electoral de cara a la votación del 2 de octubre. A pesar de que en su discurso de apertura de la 77ª Asamblea General de las Naciones Unidas Jair Messias Bolsonaro dijo al mundo que la Amazonia “está preservada en más de un 80%”, los datos cuentan una realidad diferente y más preocupante. Según un reciente estudio del Instituto Nacional de Investigaciones Espaciales (Inpe), en 2022 y hasta la fecha del 19 de septiembre, se registraron más de 76.000 incendios, la cifra más alta desde 2010. El resultado es que, siempre según el Inpe, de agosto de 2020 a junio de 2021 se han deforestado 13 mil kilómetros cuadrados de Amazonia, el equivalente a nueve veces la ciudad de São Paulo.
+    <t xml:space="preserve">**** *pais_ag *jornal_infobae *ano_2022
+    La Amazonia y el lobby del agronegocio en el centro de la campaña electoral de Brasil. La llamada bancada ruralista ha apoyado a Bolsonaro desde las elecciones de 2018 mientras que Lula agita la causa medioambiental
+. La cuestión medioambiental, por un lado, y el lobby del agronegocio, por otro, han sido la cruz y la alegría del gobierno de Bolsonaro y vuelven a salir, inevitablemente, a la luz en esta campaña electoral de cara a la votación del 2 de octubre. A pesar de que en su discurso de apertura de la 77ª Asamblea General de las Naciones Unidas Jair Messias Bolsonaro dijo al mundo que la Amazonia “está preservada en más de un 80%”, los datos cuentan una realidad diferente y más preocupante. Según un reciente estudio del Instituto Nacional de Investigaciones Espaciales (Inpe), en 2022 y hasta la fecha del 19 de septiembre, se registraron más de 76.000 incendios, la cifra más alta desde 2010. El resultado es que, siempre según el Inpe, de agosto de 2020 a junio de 2021 se han deforestado 13 mil kilómetros cuadrados de Amazonia, el equivalente a nueve veces la ciudad de São Paulo.
 “La delincuencia en la Amazonia no es sólo ambiental, sino que ahora se ha convertido en multidimensional”, explica a Infobae Alexandre Saraiva, el ex superintendente de la Policía Federal del Estado de Amazonas que el año pasado denunció al ministro de Medio Ambiente, Ricardo Salles, acusado de connivencia con los madereros ilegales de la región. “Esta delincuencia se nutre del tráfico de madera, de la pesca y la minería ilegales, de las drogas. Si no se detiene, tendremos un enorme problema de seguridad pública, los diversos grupos criminales se unirán, creando una tierra de nadie en la que Brasil corre el riesgo de perder su soberanía y en la que se destruirá el patrimonio natural de la Amazonia”.
 Pero el tema sigue siendo tabú. Porque detrás de la deforestación está el tráfico de madera, que forma parte de un gigantesco sector de agronegocio que por sí solo representa el 27% del PIB de Brasil. Según Imaflora, una ONG de conservación del medio ambiente, sólo el 10% de la madera amazónica es legal. “El agronegocio es importante para la economía brasileña, pero debe aprender a respetar la ley”, explica Saraiva, “y liberarse de actividades ilegales como el tráfico de madera, que por sí solo representa menos del 0,01% del PIB de Brasil, pero es la principal causa de deforestación en la Amazonia.”
 La llamada bancada ruralista, es decir el bloque político que representa el lobby del agronegocio en el Congreso, es extremadamente poderoso, a menudo se mezcla con el lobby de las armas y ha apoyado a Bolsonaro desde las elecciones de 2018. Entre los principales donantes de la campaña presidencial de este año están los productores rurales Oscar Luiz Cervi, con un millón de reales, y Odílio Balbinotti Filho, con 600 mil. En el 200º aniversario de la independencia de Brasil, el 7 de septiembre, los tractores también participaron en la procesión oficial con el presidente, como símbolo de este lobby. La importancia del sector para la economía brasileña seguramente también pesó en la decisión del gobierno de no sancionar a la Rusia de Putin, ya que el país depende de Moscú para los fertilizantes, especialmente el cloruro de potasio.
@@ -104,10 +100,9 @@
     <t>https://www.infobae.com/america/agencias/2023/12/14/brasil-espera-exportar-92000-millones-de-dolares-con-proyectos-de-agronegocio/</t>
   </si>
   <si>
-    <t xml:space="preserve">**** pais_ag jornal_infobae *ano_2023
-    Brasil espera exportar 92.000 millones de dólares con proyectos de agronegocio
-    Brasil espera exportar 92.000 millones de dólares con proyectos de agronegocio
-    São Paulo, 14 dic (EFE).- Brasil, uno de los mayores productores de alimentos del mundo y el mayor exportador mundial de maíz, soja, café, zumo de naranja y azúcar, espera alcanzar en 2024 la cifra récord de 92.000 millones de dólares en ventas al extranjero con proyectos para la promoción del agronegocio.
+    <t xml:space="preserve">**** *pais_ag *jornal_infobae *ano_2023
+    Brasil espera exportar 92.000 millones de dólares con proyectos de agronegocio. Brasil espera exportar 92.000 millones de dólares con proyectos de agronegocio
+. São Paulo, 14 dic (EFE).- Brasil, uno de los mayores productores de alimentos del mundo y el mayor exportador mundial de maíz, soja, café, zumo de naranja y azúcar, espera alcanzar en 2024 la cifra récord de 92.000 millones de dólares en ventas al extranjero con proyectos para la promoción del agronegocio.
 "Nuestra estimación es cerrar 2023 con 89.000 millones de dólares en exportaciones de nuestros proyectos. Pero queremos llegar a 2024 con 92.000 millones de dólares, otro récord", dijo a EFE el gerente de Agronegocios de la Agencia Brasileña de Promoción de Exportaciones e Inversiones (ApexBrasil), Laudemir Müller.
 Actualmente son 21 los proyectos sectoriales vigentes llevados a cabo por ApexBrasil e instituciones asociadas, que tienen como objetivo impulsar la agroindustria brasileña en el mercado extranjero, y se espera que en 2024 se firmen seis convenios más, con una duración estimada de dos años.
 "La expectativa de ApexBrasil para el próximo año es apoyar a cerca de 2.254 empresarios, productores y cooperativas brasileñas del sector agroindustrial que deseen entrar en el mercado internacional”, añadió Müller.
